--- a/temu-trial/SKU-image-report.xlsx
+++ b/temu-trial/SKU-image-report.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="试跑汇总" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片URL明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="160款价格与材料" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本次填写规则" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'试跑汇总'!$A$1:$H$4</definedName>
@@ -57,9 +59,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -435,8 +438,15 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +490,41 @@
           <t>商品链接</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>商品产地</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>产地省份（用户指定）</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>核算表材料</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>30%毛利定价原值</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>换算汇率</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>人民币申报价格</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>币种</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,12 +555,41 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>原图仅2张，少于3张轮播图；产地、规格、食品接触材质、申报价格及其他必填字段待确认，库存为10.9表格快照，未作为实时库存填写</t>
+          <t>产地、价格、材料、食品接触材质、圆形规格、包装尺寸及重量已补充；仅2张原图，不足3张；库存引用10.9表格，未验证实时库存；尚未测试TEMU导入</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>https://www.lakeside.com/products/summer-dining-melamine-plates-set-of-4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>22.0742791523277</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CNY</t>
         </is>
       </c>
     </row>
@@ -556,6 +630,35 @@
           <t>https://www.lakeside.com/products/christmas-table-sentiment-word-decor-set-of-4</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>21.9141378859067</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -592,6 +695,35 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>https://www.lakeside.com/products/individual-snack-and-dip-bowls-chips-serving-bowls-set-of-6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>14.2277994768866</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CNY</t>
         </is>
       </c>
     </row>
@@ -994,4 +1126,8002 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K161"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>核算表材料</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>30%毛利定价原值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>人民币申报价格</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>币种</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>商品产地</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>省份</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>核算表行号</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2139311</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>向日葵密胺餐盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>22.0742791523277</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2818</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2142880</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>节日寄语餐位餐具 4 件套</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>21.9141378859067</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2950</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2135291</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>零食蘸料小碗 6 件套</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.2277994768866</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5571</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2144645</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5 英寸沙拉蘸料碗三件套</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.8977772288999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>125.28</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3017</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2142684</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>待客点心收纳托盘</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>铝、聚丙烯（PP）、聚苯乙烯（聚苯乙烯（PS））</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>33.4782248060444</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>234.35</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3099</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2140659</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>瓶身置物托盘两件装</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>聚乙烯</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17.4859222039331</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3074</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2139303</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>庭院美好生活主题托盘</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>33.7529422824186</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>236.27</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3135</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2139294</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>二合一点心托盘 - 红色</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>白云石</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>34.288516020578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>240.02</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3242</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2141193</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>丰收格纹双层点心托盘</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>三聚氰胺和金属</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20.3658107243775</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>142.56</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3244</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2140603</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>惠尔通备料搅拌碗 3 件套</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>硅胶</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>18.6903732758732</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>130.83</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3190</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2146089</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>爱国主题纸质餐具 36 件套</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>纸</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>29.782883980528</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>208.48</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3276</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2139013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>正餐餐盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>31.5748146154711</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>221.02</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3211</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2148769</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4个装8英寸密胺餐盘</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24.9904427662708</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>174.93</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3376</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2146518</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蓝款 12 件套密胺餐具</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>40.8720031114003</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3519</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2139011</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>沙拉碗 4 件套</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>23.677903712483</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>165.75</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3406</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2139563</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12 件套密胺餐具套装 - 绿色</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>42.3892162699693</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>296.72</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3480</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2141194</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>丰收格纹餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>22.2586038144146</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>155.81</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3487</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2148784</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6个装单人小食托盘</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>18.5390795932323</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3101</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2148794</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13英寸上菜托盘</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>28.9254056525001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>202.48</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>3553</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2138869</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>四格蝴蝶摆盘配小勺</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>41.7620700396851</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>292.33</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3349</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2150164</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18 英寸清新绿色上菜大浅盘</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>28.250040090614</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>197.75</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3574</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2139694</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>装饰餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21.523222142553</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>150.66</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3658</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2150165</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12英寸清新绿色沙拉碗</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>26.8254316422774</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>187.78</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3653</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2148788</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>乡村木屋风 4 个装密胺沙拉盘</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>24.5111986448451</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>171.58</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>3699</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2141060</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>搅拌碗 + 量杯套装</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25.2592618534582</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>176.81</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>3734</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2146087</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>向日葵零食蘸料拼盘套装</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>30.8696621881918</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>216.09</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>3729</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2148781</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>绣球花 4 个装密胺沙拉盘</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>21.7952853437931</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>152.57</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>3772</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2148525</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12英寸圆形密胺大餐盘</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>23.0918987467766</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>161.64</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3796</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2148775</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12件套托斯卡纳风餐具套装</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>29.1547055321361</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>204.08</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3790</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2140919</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>分杯加盖分体零食碗粉色</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>硅胶</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20.2202679711937</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>141.54</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3723</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2148773</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14英寸上菜大盘</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18.096700404224</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3828</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2146981</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>人字拖图案密胺餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>21.0071130887099</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>147.05</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3665</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2149211</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>波浪边缘三聚氰胺餐具 12件套装</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>39.3770563720114</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>275.64</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3884</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2148212</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>湖畔生活餐具套装（上菜拼盘）</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.6126546253509</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>158.29</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3927</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2148070</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>美式复古派对餐盘三件套</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>25.1816980356521</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>176.27</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>3960</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2139014</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>大号上菜碗</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>24.4113684078589</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>170.88</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>3849</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2144716</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>甜点餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>24.5073646918737</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3976</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2146856</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>骷髅塑料上菜托盘两件装</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.9163645278247</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>4073</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2146086</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>鸢尾花零食蘸料拼盘套装</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>30.246792290068</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>211.73</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4084</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2147577</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>清新柑橘风沙拉碗配餐具套装</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>31.3254602126001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>4129</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2144329</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>微波炉煮饭器皿</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>22.7601143550204</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>159.32</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>4122</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2148776</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>萌猫节日主题大餐盘</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>22.0239953845105</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>154.17</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>4057</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2146980</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>鲜果藤蔓串珠上菜托盘</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>32.8670042265645</v>
+      </c>
+      <c r="E44" t="n">
+        <v>7</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>230.07</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>4099</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2144518</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>多莉・帕顿餐具套装 蓝色款</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>41.7026437686283</v>
+      </c>
+      <c r="E45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>291.92</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>4156</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2144296</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>兔子造型点心摆盘</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>26.2196670727953</v>
+      </c>
+      <c r="E46" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>183.54</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>4247</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2148777</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4个装密胺甜品盘</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18.1297313836699</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>126.91</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>4048</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2148211</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>13英寸大餐盘</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>29.9645543674807</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>209.75</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>4258</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2148778</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4件套万圣节沙拉盘</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18.5682766197069</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>129.98</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2148787</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>乡村木屋风 4 个装密胺正餐盘</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>29.8654614291428</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>209.06</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>4348</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2148101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>塔可饼餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>25.7976373264814</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>180.58</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>4382</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2146978</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>船锚主题正餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>25.3857823015146</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>4292</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2144517</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>多莉・帕顿餐具套装 红色款</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>41.7026437686283</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>291.92</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>4253</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2146104</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>开胃小食盘四件套</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>25.6482606203262</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>179.54</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2148782</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>绣球花 4 个装密胺正餐盘</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>23.9925827755976</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>167.95</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>4464</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2148580</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>多彩微波炉托盘四件套</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>25.5560982892828</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>178.89</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>4511</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2146977</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>船锚主题大餐盘</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>21.6910313149168</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>151.84</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>4252</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2146084</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>向日葵蝴蝶椭圆形大餐盘</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>27.6516485076154</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>4544</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2146971</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>清新柑橘甜品盘四件套</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>23.2762234088634</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>4653</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2148247</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>爪印蘸料小碗三件套</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>陶瓷和不锈钢</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>33.6771479813685</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>235.74</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>4550</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2146948</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>海边风贝壳甜品盘四件套</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>26.0169099444998</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>182.12</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>4566</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2147528</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>复活节花卉餐具——沙拉盘、餐盘、餐巾架</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>22.0450821258532</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>154.32</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>4746</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2142260</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>木质桌面点心托盘（原木款）</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>木材和金属</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>29.4249992166202</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>205.97</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>4849</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2139559</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>双层冷藏点心托盘</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>聚苯乙烯（聚苯乙烯（PS））和聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>32.1491702625336</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>225.04</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>4236</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2148038</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>祈福厨房主题派盘</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>37.9235458166596</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>265.46</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4987</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2146979</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>鲜果藤蔓开胃小食盘</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>23.6200994984526</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>165.34</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>4795</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2142261</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>木质桌面点心托盘（白色款）</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>木材和金属</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>29.7364341656821</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>208.16</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>4902</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2139709</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>圆形点心托盘</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>34.5110327526492</v>
+      </c>
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>241.58</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>4412</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2139312</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>露营车密胺餐盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>21.7609272267802</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>152.33</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>4663</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2101781</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>两件微波炉餐盘隔热套</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>聚脂钎维</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>18.3052084619766</v>
+      </c>
+      <c r="E70" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>4079</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2148037</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>家之寄语派盘</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>37.9235458166596</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>265.46</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5106</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2139020</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>小点心盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>20.4337896597551</v>
+      </c>
+      <c r="E72" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>143.04</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>4381</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2132539</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>节日装饰餐盘 - 黑色</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>白云石</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>19.6469445422389</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>137.53</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>4966</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2143988</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>情人节点心摆盘</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>21.785110622446</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>5029</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2143939</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>9 英寸密胺餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>24.4704997594563</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>171.29</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>5132</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2148251</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>平底锅形状陶瓷蘸碗 -一套 6件</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>35.5000451595422</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>5205</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2133946</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>带勺双格蘸料碗 - 藏青色</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>27.2315357377871</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>190.62</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5243</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2146976</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>船锚主题沙拉盘四件套</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>23.7884985097351</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>166.52</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>4951</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2146405</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>天堂火烈鸟甜品盘套装</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>25.4881193539052</v>
+      </c>
+      <c r="E79" t="n">
+        <v>7</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>178.42</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>5115</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2148250</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>柠檬棕榈蘸料碗六件套</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>36.122915057666</v>
+      </c>
+      <c r="E80" t="n">
+        <v>7</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>252.86</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>5286</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2146947</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>海边风海星沙拉盘四件套</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>24.4044378005644</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>170.83</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5280</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2146101</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>夏日柠檬款上菜托盘</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）和金属</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>31.5202545154934</v>
+      </c>
+      <c r="E82" t="n">
+        <v>7</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>220.64</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5391</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2150377</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>花卉图案小食托盘配小抹铲</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>石器和竹材</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>24.155230857423</v>
+      </c>
+      <c r="E83" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>169.09</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5398</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2146085</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>向日葵蝴蝶密胺餐盘</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>23.4770635606732</v>
+      </c>
+      <c r="E84" t="n">
+        <v>7</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>164.34</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>4900</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2133947</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>带勺双格蘸料碗 - 青绿色</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>27.2315357377871</v>
+      </c>
+      <c r="E85" t="n">
+        <v>7</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>190.62</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>5091</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2148443</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>18盎司马克杯蘸料碗两件套装</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>35.2032087237176</v>
+      </c>
+      <c r="E86" t="n">
+        <v>7</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>5568</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2148589</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>趣味印花纸盘8个装</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>纸板和聚丙烯</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>17.8610597562122</v>
+      </c>
+      <c r="E87" t="n">
+        <v>7</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>125.03</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>4584</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2146102</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>夏日菠萝款上菜托盘</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）和金属</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>31.7598765762063</v>
+      </c>
+      <c r="E88" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>222.32</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>82</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2137060</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>带勺双格蘸料碗 - 芥末黄</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>27.2480512275101</v>
+      </c>
+      <c r="E89" t="n">
+        <v>7</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>190.74</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>188</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2150382</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>长方形木质餐用摆盘</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>32.3112285054403</v>
+      </c>
+      <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>226.18</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>189</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2148839</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>黑色镀锌上菜托盘</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>铁</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>29.9017365226415</v>
+      </c>
+      <c r="E91" t="n">
+        <v>7</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>209.31</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>5539</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2150379</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>湖畔印花三件粗陶餐碗套装</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>石器和皮革</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>30.724119435008</v>
+      </c>
+      <c r="E92" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>164</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2138506</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5 英寸兔子造型小碗</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>30.8013883333548</v>
+      </c>
+      <c r="E93" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>215.61</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>5526</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2146406</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>天堂火烈鸟 12 英寸大餐盘</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>30.2525432195251</v>
+      </c>
+      <c r="E94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>211.77</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>135</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2139711</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>15 英寸大餐盘</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>42.1610960681706</v>
+      </c>
+      <c r="E95" t="n">
+        <v>7</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>295.13</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>5150</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2148384</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>12件套绿色密胺餐具套装</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三聚氰胺
+</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>43.0723971975278</v>
+      </c>
+      <c r="E96" t="n">
+        <v>7</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>301.51</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>245</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2152302</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MDZ 12 件套密胺餐具 浅蓝色</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>8.13977707775368</v>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>461</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2148587</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>趣味烫金正餐盘8个装</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>纸板和聚丙烯</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>22.212891298217</v>
+      </c>
+      <c r="E98" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>155.49</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>5037</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2147955</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>海龟12 件套密胺餐具</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>41.4292534298212</v>
+      </c>
+      <c r="E99" t="n">
+        <v>7</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>272</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2146570</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>一次性金色纸质沙拉盘和餐巾纸套装，用于庆祝活动</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>纸</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>23.501246956339</v>
+      </c>
+      <c r="E100" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>164.51</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>568</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2148780</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4件套万圣节装饰底盘</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>20.4795021759526</v>
+      </c>
+      <c r="E101" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>143.36</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>5292</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2148045</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>欢聚主题派盘</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>38.9761133670402</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>272.83</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>627</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2150378</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>海洋印花三件粗陶餐碗套装</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>石器和皮革</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>30.724119435008</v>
+      </c>
+      <c r="E103" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>501</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2140918</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>分杯加盖分体零食碗米色</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>硅胶</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>20.5317029202556</v>
+      </c>
+      <c r="E104" t="n">
+        <v>7</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>143.72</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>129</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2146973</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>美式复古沙拉盘四件套</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>21.8937884432123</v>
+      </c>
+      <c r="E105" t="n">
+        <v>7</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>153.26</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>5114</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2148847</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>派对大号沙拉蘸酱碗</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>17.8609122964825</v>
+      </c>
+      <c r="E106" t="n">
+        <v>7</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>125.03</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>379</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2148383</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12件套黄色密胺餐具套装</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>42.6853154071455</v>
+      </c>
+      <c r="E107" t="n">
+        <v>7</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>713</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2139539</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>祈福之家旋转置物盘</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>25.2922928329042</v>
+      </c>
+      <c r="E108" t="n">
+        <v>7</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>4903</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2148029</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>25个装可折叠一次性餐盘</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>甘蔗浆纤维</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>33.830358640495</v>
+      </c>
+      <c r="E109" t="n">
+        <v>7</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>236.81</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>788</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2144715</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>16 英寸点心摆盘两件装</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>34.484342541579</v>
+      </c>
+      <c r="E110" t="n">
+        <v>7</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>241.39</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>651</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2136443</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>密胺长方形蘸料托盘</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>15.7717028465258</v>
+      </c>
+      <c r="E111" t="n">
+        <v>7</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>996</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2139710</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>双层点心托盘</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）和铁</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>46.4831407447822</v>
+      </c>
+      <c r="E112" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>730</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2152569</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LS6 “保佑阖家” 印花旋转餐桌转盘</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>8.13977707775368</v>
+      </c>
+      <c r="E113" t="n">
+        <v>7</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>1184</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2143858</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>薄饼烘烤碗两件装</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>碳钢</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>21.3776793893693</v>
+      </c>
+      <c r="E114" t="n">
+        <v>7</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>149.64</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>1003</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2148047</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>欢聚带把手上菜托盘</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>39.7286003675434</v>
+      </c>
+      <c r="E115" t="n">
+        <v>7</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>1442</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2138871</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>多莉·帕顿餐具——杯子、蘸碗、托盘或调味品套装</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>34.305031510301</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>240.14</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>4984</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2146946</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>海边风正餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>28.353999200031</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>198.48</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>570</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2122158</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>冷热两用带盖蘸料摆盘</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>23.6130214314285</v>
+      </c>
+      <c r="E118" t="n">
+        <v>7</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>165.29</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>1816</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2142750</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>红色可叠放点心碗</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>陶器</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>55.8033329585399</v>
+      </c>
+      <c r="E119" t="n">
+        <v>7</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>390.62</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1828</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2137059</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>带勺双格蘸料碗 - 红色</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>27.2480512275101</v>
+      </c>
+      <c r="E120" t="n">
+        <v>7</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>190.74</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>1830</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2143304</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>感恩主题派盘</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>40.4779907137235</v>
+      </c>
+      <c r="E121" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>283.35</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>2054</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2139540</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>家庭主题旋转置物盘</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25.2922928329042</v>
+      </c>
+      <c r="E122" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5275</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2139009</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>贝壳造型餐盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>21.5581700984847</v>
+      </c>
+      <c r="E123" t="n">
+        <v>7</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>150.91</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2146519</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>多色混搭 12 件套密胺餐具</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>40.5605681623384</v>
+      </c>
+      <c r="E124" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>2111</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2129052</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>带盖陶瓷碗 6 件套 - 红色</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>聚丙烯（PP）</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>27.3789954674566</v>
+      </c>
+      <c r="E125" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>191.65</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>2209</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2147651</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>带盖陶瓷黄油碟</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>陶瓷和木材</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>25.3679396742246</v>
+      </c>
+      <c r="E126" t="n">
+        <v>7</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1333</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2139010</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>正餐餐盘 4 件套</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>25.1797810591664</v>
+      </c>
+      <c r="E127" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>176.26</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1894</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2146967</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12 件套密胺家用仿瓷餐具套装</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>40.099019208473</v>
+      </c>
+      <c r="E128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>280.69</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>2222</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2148793</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>哥特风12件套密胺餐具</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>41.7886127910256</v>
+      </c>
+      <c r="E129" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>292.52</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>132</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2057855</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>曼陀罗三聚氰胺12件套餐具套装</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>三聚氰胺和塑料</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>41.4338246814409</v>
+      </c>
+      <c r="E130" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>290.04</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>818</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2139293</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>二合一爱国主题点心托盘</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>白云石</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>31.6342408865279</v>
+      </c>
+      <c r="E131" t="n">
+        <v>7</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>221.44</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>965</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2146853</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5 英寸迷你派盘 4 个装</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>20.0359433091069</v>
+      </c>
+      <c r="E132" t="n">
+        <v>7</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1268</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2004299</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>双层餐用托盘</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>38.9780303435259</v>
+      </c>
+      <c r="E133" t="n">
+        <v>7</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>272.85</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1588</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2141159</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>姜饼人旋转餐桌转盘</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>白云石和竹材</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>49.7515856529056</v>
+      </c>
+      <c r="E134" t="n">
+        <v>7</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>348.26</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>1645</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2148205</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>8件套密胺餐具</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>塑料和金属</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>31.2091144858909</v>
+      </c>
+      <c r="E135" t="n">
+        <v>7</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>218.46</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1652</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2148408</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>智能家居搅拌碗六件套</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>26.0054080855856</v>
+      </c>
+      <c r="E136" t="n">
+        <v>7</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>182.04</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1774</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2144070</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>爱心造型餐盘四件套</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>24.2696596076465</v>
+      </c>
+      <c r="E137" t="n">
+        <v>7</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>169.89</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>2398</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2144896</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>16 件套 Gibson 品牌不锈钢西餐餐具</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>19.8681341367431</v>
+      </c>
+      <c r="E138" t="n">
+        <v>7</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>139.08</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>2409</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2142147</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>木质点心托盘</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>中密度纤维板（MDF）和铁</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>24.4317178505533</v>
+      </c>
+      <c r="E139" t="n">
+        <v>7</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>171.02</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>2431</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2139797</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>汤碗配菜碗 2 件套 - 橙色</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>28.4676906516061</v>
+      </c>
+      <c r="E140" t="n">
+        <v>7</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>199.27</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>2476</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2139730</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>黄油碟</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>24.8740970395616</v>
+      </c>
+      <c r="E141" t="n">
+        <v>7</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>174.12</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>2498</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2140605</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>惠尔通硅胶搅拌厨具</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>硅胶和塑料</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>17.0886656922036</v>
+      </c>
+      <c r="E142" t="n">
+        <v>7</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>2502</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2141179</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>雪人节日点心托盘</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>46.7031506614491</v>
+      </c>
+      <c r="E143" t="n">
+        <v>7</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>2508</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2128349</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>双层点心托盘</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>32.0919558874219</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>224.64</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>2580</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2128351</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>三格调味托盘</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>35.4243983182218</v>
+      </c>
+      <c r="E145" t="n">
+        <v>7</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>247.97</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>2611</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2128352</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>上菜大碗</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>41.9176400544864</v>
+      </c>
+      <c r="E146" t="n">
+        <v>7</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>293.42</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>2612</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2117253</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>两件汤碗 红米白配色</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>28.1232247230983</v>
+      </c>
+      <c r="E147" t="n">
+        <v>7</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>196.86</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>2679</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2115814</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>格纹四件套正餐餐盘</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>42.7406128057716</v>
+      </c>
+      <c r="E148" t="n">
+        <v>7</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>2700</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2138868</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3D 吉他造型零食蘸料摆盘</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>34.6620315158307</v>
+      </c>
+      <c r="E149" t="n">
+        <v>7</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>242.63</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>235</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2138262</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>11 英寸不锈钢正餐圆盘</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>不锈钢</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>17.7318850330218</v>
+      </c>
+      <c r="E150" t="n">
+        <v>7</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>124.12</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>322</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2139015</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>点心摆盘</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>18.6128094580671</v>
+      </c>
+      <c r="E151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>589</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2136654</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>银色搅拌碗 5 件套</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>不锈钢和塑料</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>22.6126546253509</v>
+      </c>
+      <c r="E152" t="n">
+        <v>7</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>158.29</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>1686</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2148248</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>蜜蜂主题白色蘸料碗六件套</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>30.8792470706203</v>
+      </c>
+      <c r="E153" t="n">
+        <v>7</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>1775</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2139725</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>秋叶开胃小食盘四件套</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>28.2821863116819</v>
+      </c>
+      <c r="E154" t="n">
+        <v>7</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>2151</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2148581</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>姜饼人甜品盘八件套</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>纸板和聚丙烯</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>15.1072493046352</v>
+      </c>
+      <c r="E155" t="n">
+        <v>7</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>2174</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2113851</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>带底座高脚碗 - 灰褐色</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>51.2521358620219</v>
+      </c>
+      <c r="E156" t="n">
+        <v>7</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>2303</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2143520</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>礼盒香草糖果小勺六件套</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>21.8626744402521</v>
+      </c>
+      <c r="E157" t="n">
+        <v>7</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>153.04</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>2390</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2136442</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>密胺圆形蘸料托盘</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>三聚氰胺</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>15.7901353127344</v>
+      </c>
+      <c r="E158" t="n">
+        <v>7</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>3768</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2143525</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>多莉帕顿乡村头巾款餐具套装</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>78.06960467889721</v>
+      </c>
+      <c r="E159" t="n">
+        <v>7</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>546.49</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>5034</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2143526</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>多莉帕顿蓝调风情餐具套装</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>石器</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>78.06960467889721</v>
+      </c>
+      <c r="E160" t="n">
+        <v>7</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>546.49</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>5469</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2125452</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CMJ 4 件套沙拉盘</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>8.13977707775368</v>
+      </c>
+      <c r="E161" t="n">
+        <v>7</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>湖南省</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>5625</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>价格已计算；尚未全量采图/类目核验/导入</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>产地：中国大陆；省份：湖南省；来源为用户指定，并非网页验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>价格：按SKU匹配产品价格核算表格.xlsx的W列（30%毛利定价），乘7后四舍五入至人民币分；币种CNY。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>材料：优先取核算表C列，映射为模板已有枚举，不修改枚举本身；缺失或不够具体时再查网页，不猜测金属型号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>样本2139311：三聚氰胺映射为材料=密胺（三聚氰胺）、食品接触材质=三聚氰胺(密胺)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>包装尺寸：核算表F/G/H列英寸乘2.54，按最长到最短排序；重量按J列kg乘1000填g。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>库存：样本使用核算表10.9库存快照1710，未当作实时库存验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>模板仅填2139311；其他两款类目不符不填，160款价格表是独立核算结果，不代表160款已经完成上架模板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>样本仍缺第3张有效轮播原图；未执行TEMU上传，未验证中国大陆网络图片访问。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/temu-trial/SKU-image-report.xlsx
+++ b/temu-trial/SKU-image-report.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>产地、价格、材料、食品接触材质、圆形规格、包装尺寸及重量已补充；仅2张原图，不足3张；库存引用10.9表格，未验证实时库存；尚未测试TEMU导入</t>
+          <t>已按用户要求将详情图复用为第3个轮播图；3个轮播图位置均已填入，但第1与第3张为同图，共2张不同原图。尚未验证TEMU是否接受重复图或国内网络访问。库存为10.9表格快照。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -9117,7 +9117,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>样本仍缺第3张有效轮播原图；未执行TEMU上传，未验证中国大陆网络图片访问。</t>
+          <t>按用户要求将详情图URL复用至第3个轮播图位置，第1与第3张重复；尚未验证TEMU是否接受重复图及中国大陆访问。未上传TEMU。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>轮播图与详情图允许共用（用户确认）；本次将BY6的图片URL填写到BQ6。</t>
         </is>
       </c>
     </row>
